--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evenement.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evenement.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7278" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7278" uniqueCount="549">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -414,9 +414,6 @@
     <t>ccdEncounterActivity</t>
   </si>
   <si>
-    <t>Conformité Encounter activity (CCD) si évènement réalisée (EVN) </t>
-  </si>
-  <si>
     <t>Conformité Encounter activity (CCD) si évènement réalisée (EVN)</t>
   </si>
   <si>
@@ -460,9 +457,6 @@
   </si>
   <si>
     <t>ccdPlanOfCareActivityPlannedRealised</t>
-  </si>
-  <si>
-    <t>Conformité Plan of care activity (CCD) si évènement planifiée (INT) </t>
   </si>
   <si>
     <t>Conformité Plan of care activity (CCD) si évènement planifiée (INT)</t>
@@ -3242,7 +3236,7 @@
         <v>129</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3313,10 +3307,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3414,10 +3408,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3517,10 +3511,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3620,10 +3614,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3652,7 +3646,7 @@
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3664,7 +3658,7 @@
         <v>75</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>75</v>
@@ -3723,10 +3717,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3826,13 +3820,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>75</v>
@@ -3857,10 +3851,10 @@
         <v>96</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3931,10 +3925,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4032,10 +4026,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4135,10 +4129,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4238,10 +4232,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4270,7 +4264,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4282,7 +4276,7 @@
         <v>75</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>75</v>
@@ -4341,10 +4335,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4444,13 +4438,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -4475,10 +4469,10 @@
         <v>96</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4549,10 +4543,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4650,10 +4644,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4753,10 +4747,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4856,10 +4850,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4888,7 +4882,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4900,7 +4894,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4959,10 +4953,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5062,10 +5056,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5079,7 +5073,7 @@
         <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>75</v>
@@ -5099,7 +5093,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>75</v>
@@ -5121,7 +5115,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -5139,7 +5133,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5159,10 +5153,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5176,7 +5170,7 @@
         <v>76</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>75</v>
@@ -5188,10 +5182,10 @@
         <v>86</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5222,7 +5216,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -5240,7 +5234,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5260,10 +5254,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5277,7 +5271,7 @@
         <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>75</v>
@@ -5289,10 +5283,10 @@
         <v>96</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5343,7 +5337,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5363,10 +5357,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5380,7 +5374,7 @@
         <v>76</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>75</v>
@@ -5389,13 +5383,13 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5422,11 +5416,11 @@
         <v>75</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5444,7 +5438,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5464,10 +5458,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5565,10 +5559,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5584,7 +5578,7 @@
         <v>76</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>75</v>
@@ -5597,7 +5591,7 @@
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5648,7 +5642,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5668,17 +5662,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>76</v>
@@ -5687,7 +5681,7 @@
         <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
@@ -5700,7 +5694,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5751,7 +5745,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5771,17 +5765,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>81</v>
@@ -5803,7 +5797,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5854,7 +5848,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5874,17 +5868,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>81</v>
@@ -5906,7 +5900,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5957,7 +5951,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5977,17 +5971,17 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>81</v>
@@ -5996,7 +5990,7 @@
         <v>76</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>75</v>
@@ -6009,7 +6003,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6060,7 +6054,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6080,10 +6074,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6106,11 +6100,11 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6161,7 +6155,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6181,10 +6175,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6211,7 +6205,7 @@
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6262,7 +6256,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6282,41 +6276,41 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E42" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="F42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="M42" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6367,7 +6361,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6387,10 +6381,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6488,17 +6482,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>81</v>
@@ -6520,7 +6514,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6551,7 +6545,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -6569,7 +6563,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6589,17 +6583,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>81</v>
@@ -6617,11 +6611,11 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6672,7 +6666,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6692,17 +6686,17 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>81</v>
@@ -6724,7 +6718,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6755,7 +6749,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>75</v>
@@ -6773,7 +6767,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6793,17 +6787,17 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>81</v>
@@ -6825,7 +6819,7 @@
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6876,7 +6870,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6896,17 +6890,17 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>81</v>
@@ -6928,7 +6922,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6955,11 +6949,11 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -6977,7 +6971,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -6997,10 +6991,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7056,7 +7050,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>75</v>
@@ -7074,7 +7068,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7094,10 +7088,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7123,13 +7117,13 @@
         <v>103</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7179,7 +7173,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7199,41 +7193,41 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E51" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="F51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7284,7 +7278,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7304,17 +7298,17 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>81</v>
@@ -7332,11 +7326,11 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7387,7 +7381,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -7399,7 +7393,7 @@
         <v>75</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>75</v>
@@ -7407,17 +7401,17 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>81</v>
@@ -7435,13 +7429,13 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7492,7 +7486,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -7512,10 +7506,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7613,17 +7607,17 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>81</v>
@@ -7641,11 +7635,11 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7696,7 +7690,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7716,10 +7710,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7744,13 +7738,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7801,7 +7795,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -7821,10 +7815,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7849,13 +7843,13 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7906,7 +7900,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -7926,17 +7920,17 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>81</v>
@@ -7954,11 +7948,11 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8009,7 +8003,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8029,10 +8023,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8046,7 +8040,7 @@
         <v>76</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>75</v>
@@ -8055,10 +8049,10 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8110,7 +8104,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8130,10 +8124,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8231,17 +8225,17 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>81</v>
@@ -8263,7 +8257,7 @@
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8294,7 +8288,7 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>75</v>
@@ -8312,7 +8306,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -8332,17 +8326,17 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>81</v>
@@ -8360,11 +8354,11 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8415,7 +8409,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -8435,17 +8429,17 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>81</v>
@@ -8467,7 +8461,7 @@
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8498,7 +8492,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>75</v>
@@ -8516,7 +8510,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -8536,17 +8530,17 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>81</v>
@@ -8568,7 +8562,7 @@
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8619,7 +8613,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -8639,17 +8633,17 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>81</v>
@@ -8671,7 +8665,7 @@
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8698,11 +8692,11 @@
         <v>75</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>75</v>
@@ -8720,7 +8714,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -8740,10 +8734,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8799,7 +8793,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>75</v>
@@ -8817,7 +8811,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8837,10 +8831,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8866,13 +8860,13 @@
         <v>103</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8922,7 +8916,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8942,17 +8936,17 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>76</v>
@@ -8961,7 +8955,7 @@
         <v>76</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>75</v>
@@ -8970,11 +8964,11 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9025,7 +9019,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -9045,17 +9039,17 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>81</v>
@@ -9073,11 +9067,11 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9128,7 +9122,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -9140,7 +9134,7 @@
         <v>75</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>75</v>
@@ -9148,10 +9142,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9165,7 +9159,7 @@
         <v>76</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>75</v>
@@ -9177,10 +9171,10 @@
         <v>92</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9211,7 +9205,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>75</v>
@@ -9229,7 +9223,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -9249,10 +9243,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9266,7 +9260,7 @@
         <v>76</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>75</v>
@@ -9275,13 +9269,13 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9332,7 +9326,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -9352,10 +9346,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9378,7 +9372,7 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -9431,7 +9425,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -9451,10 +9445,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9477,7 +9471,7 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -9506,11 +9500,11 @@
         <v>75</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -9528,7 +9522,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -9548,10 +9542,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9574,7 +9568,7 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -9627,7 +9621,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -9647,10 +9641,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9673,7 +9667,7 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9726,7 +9720,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -9746,10 +9740,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9772,10 +9766,10 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -9827,7 +9821,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -9847,10 +9841,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9873,10 +9867,10 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -9928,7 +9922,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -9948,10 +9942,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9974,10 +9968,10 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -10029,7 +10023,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -10049,10 +10043,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10075,10 +10069,10 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -10130,7 +10124,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -10150,10 +10144,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10167,7 +10161,7 @@
         <v>82</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>75</v>
@@ -10176,7 +10170,7 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -10217,7 +10211,7 @@
         <v>75</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AC80" s="2"/>
       <c r="AD80" t="s" s="2">
@@ -10227,7 +10221,7 @@
         <v>125</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -10247,13 +10241,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>75</v>
@@ -10275,10 +10269,10 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -10330,7 +10324,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -10350,10 +10344,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10451,10 +10445,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10552,10 +10546,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10653,10 +10647,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10754,10 +10748,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10857,10 +10851,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10960,10 +10954,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11063,10 +11057,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11166,10 +11160,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11267,10 +11261,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11307,7 +11301,7 @@
         <v>75</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>75</v>
@@ -11326,7 +11320,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>75</v>
@@ -11344,7 +11338,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -11364,10 +11358,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11394,7 +11388,7 @@
       </c>
       <c r="L92" s="2"/>
       <c r="M92" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11445,7 +11439,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -11465,10 +11459,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11495,12 +11489,12 @@
       </c>
       <c r="L93" s="2"/>
       <c r="M93" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
@@ -11546,7 +11540,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -11566,10 +11560,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11645,7 +11639,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -11665,10 +11659,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11691,7 +11685,7 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11744,7 +11738,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -11764,10 +11758,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11790,7 +11784,7 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11843,7 +11837,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -11863,10 +11857,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11889,7 +11883,7 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11942,7 +11936,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -11962,10 +11956,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11988,7 +11982,7 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -12041,7 +12035,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -12061,10 +12055,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12087,7 +12081,7 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -12140,7 +12134,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -12160,10 +12154,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12186,7 +12180,7 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -12239,7 +12233,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -12259,10 +12253,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12285,7 +12279,7 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -12338,7 +12332,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -12358,10 +12352,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12384,7 +12378,7 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -12437,7 +12431,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -12457,10 +12451,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12483,7 +12477,7 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12536,7 +12530,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -12556,10 +12550,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12582,7 +12576,7 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12635,7 +12629,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -12655,10 +12649,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12681,7 +12675,7 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12734,7 +12728,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -12754,13 +12748,13 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>75</v>
@@ -12782,10 +12776,10 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
@@ -12837,7 +12831,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -12857,10 +12851,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12958,10 +12952,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13059,10 +13053,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13160,10 +13154,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13261,10 +13255,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13364,10 +13358,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13467,10 +13461,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13570,10 +13564,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13673,10 +13667,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13774,10 +13768,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13814,7 +13808,7 @@
         <v>75</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>75</v>
@@ -13833,7 +13827,7 @@
       </c>
       <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>75</v>
@@ -13851,7 +13845,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -13871,10 +13865,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13901,7 +13895,7 @@
       </c>
       <c r="L117" s="2"/>
       <c r="M117" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13913,7 +13907,7 @@
         <v>75</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>75</v>
@@ -13952,7 +13946,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -13972,10 +13966,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14002,12 +13996,12 @@
       </c>
       <c r="L118" s="2"/>
       <c r="M118" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
@@ -14053,7 +14047,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -14073,10 +14067,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14152,7 +14146,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -14172,10 +14166,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14198,7 +14192,7 @@
         <v>75</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -14251,7 +14245,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -14271,10 +14265,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14297,7 +14291,7 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -14350,7 +14344,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -14370,10 +14364,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14396,7 +14390,7 @@
         <v>75</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -14449,7 +14443,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -14469,10 +14463,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14495,7 +14489,7 @@
         <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -14548,7 +14542,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -14568,10 +14562,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14594,7 +14588,7 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -14647,7 +14641,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -14667,10 +14661,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14693,7 +14687,7 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -14746,7 +14740,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -14766,10 +14760,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14792,7 +14786,7 @@
         <v>75</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14845,7 +14839,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -14865,10 +14859,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14891,7 +14885,7 @@
         <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -14944,7 +14938,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -14964,10 +14958,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14990,7 +14984,7 @@
         <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -15043,7 +15037,7 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -15063,10 +15057,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15089,7 +15083,7 @@
         <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -15142,7 +15136,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -15162,10 +15156,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15188,7 +15182,7 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -15241,7 +15235,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -15261,13 +15255,13 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>75</v>
@@ -15289,10 +15283,10 @@
         <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
@@ -15344,7 +15338,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -15364,10 +15358,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15465,10 +15459,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15566,10 +15560,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15667,10 +15661,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15768,10 +15762,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15871,10 +15865,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15974,10 +15968,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16077,10 +16071,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16180,10 +16174,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16281,10 +16275,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16321,7 +16315,7 @@
         <v>75</v>
       </c>
       <c r="S141" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="T141" t="s" s="2">
         <v>75</v>
@@ -16340,7 +16334,7 @@
       </c>
       <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>75</v>
@@ -16358,7 +16352,7 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -16378,10 +16372,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16408,7 +16402,7 @@
       </c>
       <c r="L142" s="2"/>
       <c r="M142" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -16459,7 +16453,7 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -16479,10 +16473,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16509,12 +16503,12 @@
       </c>
       <c r="L143" s="2"/>
       <c r="M143" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q143" s="2"/>
       <c r="R143" t="s" s="2">
@@ -16560,7 +16554,7 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -16580,10 +16574,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16659,7 +16653,7 @@
         <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -16679,10 +16673,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16705,7 +16699,7 @@
         <v>75</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16758,7 +16752,7 @@
         <v>75</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -16778,10 +16772,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16804,7 +16798,7 @@
         <v>75</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16857,7 +16851,7 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -16877,10 +16871,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16903,7 +16897,7 @@
         <v>75</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
@@ -16956,7 +16950,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -16976,10 +16970,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17002,7 +16996,7 @@
         <v>75</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
@@ -17055,7 +17049,7 @@
         <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -17075,10 +17069,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17101,7 +17095,7 @@
         <v>75</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
@@ -17154,7 +17148,7 @@
         <v>75</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -17174,10 +17168,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17200,7 +17194,7 @@
         <v>75</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
@@ -17253,7 +17247,7 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -17273,10 +17267,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17299,7 +17293,7 @@
         <v>75</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
@@ -17352,7 +17346,7 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -17372,10 +17366,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17398,7 +17392,7 @@
         <v>75</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -17451,7 +17445,7 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -17471,10 +17465,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17497,7 +17491,7 @@
         <v>75</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -17550,7 +17544,7 @@
         <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -17570,10 +17564,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17596,7 +17590,7 @@
         <v>75</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17649,7 +17643,7 @@
         <v>75</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -17669,10 +17663,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17695,7 +17689,7 @@
         <v>75</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17748,7 +17742,7 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -17768,13 +17762,13 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>75</v>
@@ -17796,10 +17790,10 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
@@ -17851,7 +17845,7 @@
         <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -17871,10 +17865,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17972,10 +17966,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18073,10 +18067,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18174,10 +18168,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18275,10 +18269,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18378,10 +18372,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18481,10 +18475,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18584,10 +18578,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18687,10 +18681,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18788,10 +18782,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18828,7 +18822,7 @@
         <v>75</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>75</v>
@@ -18847,7 +18841,7 @@
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>75</v>
@@ -18865,7 +18859,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>76</v>
@@ -18885,10 +18879,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18915,7 +18909,7 @@
       </c>
       <c r="L167" s="2"/>
       <c r="M167" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -18966,7 +18960,7 @@
         <v>75</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -18986,10 +18980,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19016,12 +19010,12 @@
       </c>
       <c r="L168" s="2"/>
       <c r="M168" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q168" s="2"/>
       <c r="R168" t="s" s="2">
@@ -19067,7 +19061,7 @@
         <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -19087,10 +19081,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19166,7 +19160,7 @@
         <v>75</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -19186,10 +19180,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19212,7 +19206,7 @@
         <v>75</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -19265,7 +19259,7 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -19285,10 +19279,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19311,7 +19305,7 @@
         <v>75</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -19364,7 +19358,7 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -19384,10 +19378,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19410,7 +19404,7 @@
         <v>75</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
@@ -19463,7 +19457,7 @@
         <v>75</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -19483,10 +19477,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19509,7 +19503,7 @@
         <v>75</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
@@ -19562,7 +19556,7 @@
         <v>75</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -19582,10 +19576,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19608,7 +19602,7 @@
         <v>75</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -19661,7 +19655,7 @@
         <v>75</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -19681,10 +19675,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19707,7 +19701,7 @@
         <v>75</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
@@ -19760,7 +19754,7 @@
         <v>75</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -19780,10 +19774,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19806,7 +19800,7 @@
         <v>75</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
@@ -19859,7 +19853,7 @@
         <v>75</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -19879,10 +19873,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -19905,7 +19899,7 @@
         <v>75</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
@@ -19958,7 +19952,7 @@
         <v>75</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -19978,10 +19972,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20004,7 +19998,7 @@
         <v>75</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
@@ -20057,7 +20051,7 @@
         <v>75</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -20077,10 +20071,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20103,7 +20097,7 @@
         <v>75</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
@@ -20156,7 +20150,7 @@
         <v>75</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -20176,10 +20170,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20202,7 +20196,7 @@
         <v>75</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
@@ -20255,7 +20249,7 @@
         <v>75</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -20275,13 +20269,13 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D181" t="s" s="2">
         <v>75</v>
@@ -20303,10 +20297,10 @@
         <v>75</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
@@ -20358,7 +20352,7 @@
         <v>75</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -20378,10 +20372,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20479,10 +20473,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20580,10 +20574,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20681,10 +20675,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20782,10 +20776,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20885,10 +20879,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -20988,10 +20982,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21091,10 +21085,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21194,10 +21188,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21295,10 +21289,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21335,7 +21329,7 @@
         <v>75</v>
       </c>
       <c r="S191" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="T191" t="s" s="2">
         <v>75</v>
@@ -21354,7 +21348,7 @@
       </c>
       <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>75</v>
@@ -21372,7 +21366,7 @@
         <v>75</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>76</v>
@@ -21392,10 +21386,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21422,7 +21416,7 @@
       </c>
       <c r="L192" s="2"/>
       <c r="M192" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -21473,7 +21467,7 @@
         <v>75</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -21493,10 +21487,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21523,12 +21517,12 @@
       </c>
       <c r="L193" s="2"/>
       <c r="M193" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q193" s="2"/>
       <c r="R193" t="s" s="2">
@@ -21574,7 +21568,7 @@
         <v>75</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -21594,10 +21588,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21673,7 +21667,7 @@
         <v>75</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -21693,10 +21687,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21719,7 +21713,7 @@
         <v>75</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
@@ -21772,7 +21766,7 @@
         <v>75</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -21792,10 +21786,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -21818,7 +21812,7 @@
         <v>75</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
@@ -21871,7 +21865,7 @@
         <v>75</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
@@ -21891,10 +21885,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -21917,7 +21911,7 @@
         <v>75</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
@@ -21970,7 +21964,7 @@
         <v>75</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
@@ -21990,10 +21984,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22016,7 +22010,7 @@
         <v>75</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
@@ -22069,7 +22063,7 @@
         <v>75</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
@@ -22089,10 +22083,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22115,7 +22109,7 @@
         <v>75</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
@@ -22168,7 +22162,7 @@
         <v>75</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -22188,10 +22182,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22214,7 +22208,7 @@
         <v>75</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
@@ -22267,7 +22261,7 @@
         <v>75</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
@@ -22287,10 +22281,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22313,7 +22307,7 @@
         <v>75</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
@@ -22366,7 +22360,7 @@
         <v>75</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
@@ -22386,10 +22380,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22412,7 +22406,7 @@
         <v>75</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
@@ -22465,7 +22459,7 @@
         <v>75</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -22485,10 +22479,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22511,7 +22505,7 @@
         <v>75</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
@@ -22564,7 +22558,7 @@
         <v>75</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -22584,10 +22578,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22610,7 +22604,7 @@
         <v>75</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
@@ -22663,7 +22657,7 @@
         <v>75</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -22683,10 +22677,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22709,7 +22703,7 @@
         <v>75</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
@@ -22762,7 +22756,7 @@
         <v>75</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -22782,13 +22776,13 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D206" t="s" s="2">
         <v>75</v>
@@ -22810,10 +22804,10 @@
         <v>75</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="M206" s="2"/>
       <c r="N206" s="2"/>
@@ -22865,7 +22859,7 @@
         <v>75</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -22885,10 +22879,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -22986,10 +22980,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23087,10 +23081,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23188,10 +23182,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23289,10 +23283,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23392,10 +23386,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23495,10 +23489,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23598,10 +23592,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23701,10 +23695,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -23802,10 +23796,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -23842,7 +23836,7 @@
         <v>75</v>
       </c>
       <c r="S216" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="T216" t="s" s="2">
         <v>75</v>
@@ -23861,7 +23855,7 @@
       </c>
       <c r="Y216" s="2"/>
       <c r="Z216" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>75</v>
@@ -23879,7 +23873,7 @@
         <v>75</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>76</v>
@@ -23899,10 +23893,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -23929,7 +23923,7 @@
       </c>
       <c r="L217" s="2"/>
       <c r="M217" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -23980,7 +23974,7 @@
         <v>75</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -24000,10 +23994,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24030,12 +24024,12 @@
       </c>
       <c r="L218" s="2"/>
       <c r="M218" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q218" s="2"/>
       <c r="R218" t="s" s="2">
@@ -24081,7 +24075,7 @@
         <v>75</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -24101,10 +24095,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24180,7 +24174,7 @@
         <v>75</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -24200,10 +24194,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24226,7 +24220,7 @@
         <v>75</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
@@ -24279,7 +24273,7 @@
         <v>75</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
@@ -24299,10 +24293,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24325,7 +24319,7 @@
         <v>75</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
@@ -24378,7 +24372,7 @@
         <v>75</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
@@ -24398,10 +24392,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24424,7 +24418,7 @@
         <v>75</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -24477,7 +24471,7 @@
         <v>75</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -24497,10 +24491,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24523,7 +24517,7 @@
         <v>75</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -24576,7 +24570,7 @@
         <v>75</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -24596,10 +24590,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24622,7 +24616,7 @@
         <v>75</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
@@ -24675,7 +24669,7 @@
         <v>75</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -24695,10 +24689,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -24721,7 +24715,7 @@
         <v>75</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
@@ -24774,7 +24768,7 @@
         <v>75</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -24794,10 +24788,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -24820,7 +24814,7 @@
         <v>75</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
@@ -24873,7 +24867,7 @@
         <v>75</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -24893,10 +24887,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -24919,7 +24913,7 @@
         <v>75</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
@@ -24972,7 +24966,7 @@
         <v>75</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -24992,10 +24986,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25018,7 +25012,7 @@
         <v>75</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
@@ -25071,7 +25065,7 @@
         <v>75</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
@@ -25091,10 +25085,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25117,7 +25111,7 @@
         <v>75</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
@@ -25170,7 +25164,7 @@
         <v>75</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -25190,10 +25184,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -25216,7 +25210,7 @@
         <v>75</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L230" s="2"/>
       <c r="M230" s="2"/>
@@ -25269,7 +25263,7 @@
         <v>75</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
@@ -25289,10 +25283,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25315,7 +25309,7 @@
         <v>75</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="L231" s="2"/>
       <c r="M231" s="2"/>
@@ -25368,7 +25362,7 @@
         <v>75</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
@@ -25388,10 +25382,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25414,7 +25408,7 @@
         <v>75</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="L232" s="2"/>
       <c r="M232" s="2"/>
@@ -25467,7 +25461,7 @@
         <v>75</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -25487,10 +25481,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -25513,7 +25507,7 @@
         <v>75</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="L233" s="2"/>
       <c r="M233" s="2"/>
@@ -25566,7 +25560,7 @@
         <v>75</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
@@ -25586,10 +25580,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -25612,7 +25606,7 @@
         <v>75</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
@@ -25665,7 +25659,7 @@
         <v>75</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evenement.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evenement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evenement.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evenement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evenement.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evenement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
